--- a/public/templates/test_input/Input_bao_cao_40.xlsx
+++ b/public/templates/test_input/Input_bao_cao_40.xlsx
@@ -759,67 +759,65 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>12/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ca 2</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>PX Khai thác 2</t>
+          <t>PX Đào lò</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Hoàng Văn E</t>
+          <t>Phạm Văn D</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="J4" s="28" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="K4" s="28" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="L4" s="28" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="M4" s="28" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="P4" s="28" t="n">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="12" t="inlineStr">
         <is>
-          <t>Băng tải bị kẹt than, phải vệ sinh.</t>
+          <t>Máy xúc hỏng, dừng sửa chữa khoảng 40 phút.</t>
         </is>
       </c>
     </row>
@@ -829,66 +827,60 @@
           <t>06/07/2026</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Ca 1</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>PX Khai thác 3</t>
+          <t>PX Đào lò</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Hoàng Văn E</t>
+          <t>Phạm Văn D</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>1090</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K5" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M5" s="28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P5" s="28" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="G5" s="28" t="n">
-        <v>1162</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J5" s="28" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K5" s="28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L5" s="28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="28" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N5" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="O5" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="P5" s="28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>23</v>
-      </c>
       <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="12" t="inlineStr">
-        <is>
-          <t>Máy khoan gặp sự cố, tiến độ chậm.</t>
-        </is>
-      </c>
+      <c r="S5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="27" t="n"/>
